--- a/backend/Combined_sheet_output_speed/GA/GA_2030_ABM.xlsx
+++ b/backend/Combined_sheet_output_speed/GA/GA_2030_ABM.xlsx
@@ -3787,7 +3787,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G26" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="27">
@@ -3814,7 +3814,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G27" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="28">
@@ -3841,7 +3841,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G28" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="29">
@@ -3868,7 +3868,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G29" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="30">
@@ -3895,7 +3895,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G30" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="31">
@@ -3922,7 +3922,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G31" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="32">
@@ -3949,7 +3949,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G32" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="33">
@@ -3976,7 +3976,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G33" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="34">
@@ -4003,7 +4003,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G34" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="35">
@@ -4030,7 +4030,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G35" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="36">
@@ -4057,7 +4057,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G36" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="37">
@@ -4084,7 +4084,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G37" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="38">
@@ -4111,7 +4111,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G38" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="39">
@@ -4138,7 +4138,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G39" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="40">
@@ -4165,7 +4165,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G40" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="41">
@@ -4192,7 +4192,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G41" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="42">
@@ -5290,10 +5290,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D82" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E82" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F82" t="n">
         <v>270.7395326192794</v>
@@ -5317,10 +5317,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D83" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E83" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F83" t="n">
         <v>270.7395326192794</v>
@@ -5344,10 +5344,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D84" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E84" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F84" t="n">
         <v>270.7395326192794</v>
@@ -5371,10 +5371,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D85" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E85" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F85" t="n">
         <v>270.7395326192794</v>
@@ -5398,10 +5398,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D86" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E86" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F86" t="n">
         <v>270.7395326192794</v>
@@ -5425,10 +5425,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D87" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E87" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F87" t="n">
         <v>270.7395326192794</v>
@@ -5452,10 +5452,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D88" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E88" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F88" t="n">
         <v>270.7395326192794</v>
@@ -5479,10 +5479,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D89" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E89" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F89" t="n">
         <v>270.7395326192794</v>
@@ -5506,10 +5506,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D90" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E90" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F90" t="n">
         <v>270.7395326192794</v>
@@ -5533,10 +5533,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D91" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E91" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F91" t="n">
         <v>270.7395326192794</v>
@@ -5560,10 +5560,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D92" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E92" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F92" t="n">
         <v>270.7395326192794</v>
@@ -5587,10 +5587,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D93" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E93" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F93" t="n">
         <v>270.7395326192794</v>
@@ -5614,10 +5614,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D94" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E94" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F94" t="n">
         <v>270.7395326192794</v>
@@ -5641,10 +5641,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D95" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E95" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F95" t="n">
         <v>270.7395326192794</v>
@@ -5668,10 +5668,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D96" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E96" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F96" t="n">
         <v>270.7395326192794</v>
@@ -5695,10 +5695,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D97" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E97" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F97" t="n">
         <v>270.7395326192794</v>
@@ -7933,16 +7933,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D82" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E82" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F82" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G82" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="83">
@@ -7960,16 +7960,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D83" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E83" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F83" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G83" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="84">
@@ -7987,16 +7987,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D84" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E84" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F84" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G84" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="85">
@@ -8014,16 +8014,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D85" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E85" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F85" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G85" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="86">
@@ -8041,16 +8041,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D86" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E86" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F86" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G86" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="87">
@@ -8068,16 +8068,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D87" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E87" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F87" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G87" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="88">
@@ -8095,16 +8095,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D88" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E88" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F88" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G88" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="89">
@@ -8122,16 +8122,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D89" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E89" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F89" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G89" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="90">
@@ -8149,16 +8149,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D90" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E90" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F90" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G90" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="91">
@@ -8176,16 +8176,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D91" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E91" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F91" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G91" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="92">
@@ -8203,16 +8203,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D92" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E92" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F92" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G92" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="93">
@@ -8230,16 +8230,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D93" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E93" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F93" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G93" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="94">
@@ -8257,16 +8257,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D94" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E94" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F94" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G94" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="95">
@@ -8284,16 +8284,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D95" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E95" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F95" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G95" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="96">
@@ -8311,16 +8311,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D96" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E96" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F96" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G96" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="97">
@@ -8338,16 +8338,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D97" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E97" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F97" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G97" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
   </sheetData>
@@ -9073,7 +9073,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G26" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="27">
@@ -9100,7 +9100,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G27" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="28">
@@ -9127,7 +9127,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G28" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="29">
@@ -9154,7 +9154,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G29" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="30">
@@ -9181,7 +9181,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G30" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="31">
@@ -9208,7 +9208,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G31" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="32">
@@ -9235,7 +9235,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G32" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="33">
@@ -9262,7 +9262,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G33" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="34">
@@ -9289,7 +9289,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G34" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="35">
@@ -9316,7 +9316,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G35" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="36">
@@ -9343,7 +9343,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G36" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="37">
@@ -9370,7 +9370,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G37" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="38">
@@ -9397,7 +9397,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G38" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="39">
@@ -9424,7 +9424,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G39" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="40">
@@ -9451,7 +9451,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G40" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="41">
@@ -9478,7 +9478,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G41" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="42">
@@ -15871,7 +15871,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G82" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="83">
@@ -15898,7 +15898,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G83" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="84">
@@ -15925,7 +15925,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G84" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="85">
@@ -15952,7 +15952,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G85" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="86">
@@ -15979,7 +15979,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G86" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="87">
@@ -16006,7 +16006,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G87" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="88">
@@ -16033,7 +16033,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G88" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="89">
@@ -16060,7 +16060,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G89" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="90">
@@ -16087,7 +16087,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G90" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G91" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="92">
@@ -16141,7 +16141,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G92" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="93">
@@ -16168,7 +16168,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G93" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="94">
@@ -16195,7 +16195,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G94" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="95">
@@ -16222,7 +16222,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G95" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="96">
@@ -16249,7 +16249,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G96" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="97">
@@ -16276,7 +16276,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G97" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
   </sheetData>
@@ -18505,10 +18505,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D82" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E82" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F82" t="n">
         <v>429.3168316831683</v>
@@ -18532,10 +18532,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D83" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E83" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F83" t="n">
         <v>429.3168316831683</v>
@@ -18559,10 +18559,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D84" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E84" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F84" t="n">
         <v>429.3168316831683</v>
@@ -18586,10 +18586,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D85" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E85" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F85" t="n">
         <v>429.3168316831683</v>
@@ -18613,10 +18613,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D86" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E86" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F86" t="n">
         <v>429.3168316831683</v>
@@ -18640,10 +18640,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D87" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E87" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F87" t="n">
         <v>429.3168316831683</v>
@@ -18667,10 +18667,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D88" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E88" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F88" t="n">
         <v>429.3168316831683</v>
@@ -18694,10 +18694,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D89" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E89" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F89" t="n">
         <v>429.3168316831683</v>
@@ -18721,10 +18721,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D90" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E90" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F90" t="n">
         <v>429.3168316831683</v>
@@ -18748,10 +18748,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D91" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E91" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F91" t="n">
         <v>429.3168316831683</v>
@@ -18775,10 +18775,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D92" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E92" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F92" t="n">
         <v>429.3168316831683</v>
@@ -18802,10 +18802,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D93" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E93" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F93" t="n">
         <v>429.3168316831683</v>
@@ -18829,10 +18829,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D94" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E94" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F94" t="n">
         <v>429.3168316831683</v>
@@ -18856,10 +18856,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D95" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E95" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F95" t="n">
         <v>429.3168316831683</v>
@@ -18883,10 +18883,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D96" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E96" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F96" t="n">
         <v>429.3168316831683</v>
@@ -18910,10 +18910,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D97" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E97" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F97" t="n">
         <v>429.3168316831683</v>
@@ -19096,10 +19096,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D6" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E6" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F6" t="n">
         <v>303.494623655914</v>
@@ -19123,10 +19123,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D7" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E7" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F7" t="n">
         <v>303.494623655914</v>
@@ -19150,10 +19150,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D8" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E8" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F8" t="n">
         <v>303.494623655914</v>
@@ -19177,10 +19177,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D9" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E9" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F9" t="n">
         <v>303.494623655914</v>
@@ -19204,10 +19204,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D10" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E10" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F10" t="n">
         <v>303.494623655914</v>
@@ -19231,10 +19231,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D11" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E11" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F11" t="n">
         <v>303.494623655914</v>
@@ -19258,10 +19258,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D12" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E12" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F12" t="n">
         <v>303.494623655914</v>
@@ -19285,10 +19285,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D13" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E13" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F13" t="n">
         <v>303.494623655914</v>
@@ -19312,10 +19312,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D14" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E14" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F14" t="n">
         <v>303.494623655914</v>
@@ -19339,10 +19339,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D15" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E15" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F15" t="n">
         <v>303.494623655914</v>
@@ -19366,10 +19366,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D16" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E16" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F16" t="n">
         <v>303.494623655914</v>
@@ -19393,10 +19393,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D17" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E17" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F17" t="n">
         <v>303.494623655914</v>
@@ -19420,10 +19420,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D18" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E18" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F18" t="n">
         <v>303.494623655914</v>
@@ -19447,10 +19447,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D19" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E19" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F19" t="n">
         <v>303.494623655914</v>
@@ -19474,10 +19474,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D20" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E20" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F20" t="n">
         <v>303.494623655914</v>
@@ -19501,10 +19501,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D21" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E21" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F21" t="n">
         <v>303.494623655914</v>
@@ -19528,10 +19528,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D22" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E22" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F22" t="n">
         <v>303.494623655914</v>
@@ -19555,10 +19555,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D23" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E23" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F23" t="n">
         <v>303.494623655914</v>
@@ -19582,10 +19582,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D24" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E24" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F24" t="n">
         <v>303.494623655914</v>
@@ -19609,10 +19609,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D25" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E25" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F25" t="n">
         <v>303.494623655914</v>
@@ -21148,10 +21148,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D82" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E82" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F82" t="n">
         <v>382.3458781362007</v>
@@ -21175,10 +21175,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D83" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E83" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F83" t="n">
         <v>382.3458781362007</v>
@@ -21202,10 +21202,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D84" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E84" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F84" t="n">
         <v>382.3458781362007</v>
@@ -21229,10 +21229,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D85" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E85" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F85" t="n">
         <v>382.3458781362007</v>
@@ -21256,10 +21256,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D86" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E86" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F86" t="n">
         <v>382.3458781362007</v>
@@ -21283,10 +21283,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D87" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E87" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F87" t="n">
         <v>382.3458781362007</v>
@@ -21310,10 +21310,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D88" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E88" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F88" t="n">
         <v>382.3458781362007</v>
@@ -21337,10 +21337,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D89" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E89" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F89" t="n">
         <v>382.3458781362007</v>
@@ -21364,10 +21364,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D90" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E90" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F90" t="n">
         <v>382.3458781362007</v>
@@ -21391,10 +21391,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D91" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E91" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F91" t="n">
         <v>382.3458781362007</v>
@@ -21418,10 +21418,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D92" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E92" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F92" t="n">
         <v>382.3458781362007</v>
@@ -21445,10 +21445,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D93" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E93" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F93" t="n">
         <v>382.3458781362007</v>
@@ -21472,10 +21472,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D94" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E94" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F94" t="n">
         <v>382.3458781362007</v>
@@ -21499,10 +21499,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D95" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E95" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F95" t="n">
         <v>382.3458781362007</v>
@@ -21526,10 +21526,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D96" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E96" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F96" t="n">
         <v>382.3458781362007</v>
@@ -21553,10 +21553,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D97" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E97" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F97" t="n">
         <v>382.3458781362007</v>
@@ -21748,7 +21748,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G6" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="7">
@@ -21775,7 +21775,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G7" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="8">
@@ -21802,7 +21802,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G8" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="9">
@@ -21829,7 +21829,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G9" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="10">
@@ -21856,7 +21856,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G10" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="11">
@@ -21883,7 +21883,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G11" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="12">
@@ -21910,7 +21910,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G12" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="13">
@@ -21937,7 +21937,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G13" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="14">
@@ -21964,7 +21964,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G14" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="15">
@@ -21991,7 +21991,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G15" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="16">
@@ -22018,7 +22018,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G16" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="17">
@@ -22045,7 +22045,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G17" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="18">
@@ -22072,7 +22072,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G18" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="19">
@@ -22099,7 +22099,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G19" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="20">
@@ -22126,7 +22126,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G20" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="21">
@@ -22153,7 +22153,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G21" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="22">
@@ -22180,7 +22180,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G22" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="23">
@@ -22207,7 +22207,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G23" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="24">
@@ -22234,7 +22234,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G24" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="25">
@@ -22261,7 +22261,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G25" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="26">
@@ -23467,10 +23467,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D70" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E70" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F70" t="n">
         <v>44.50312779267203</v>
@@ -23494,10 +23494,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D71" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E71" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F71" t="n">
         <v>44.50312779267203</v>
@@ -23521,10 +23521,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D72" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E72" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F72" t="n">
         <v>44.50312779267203</v>
@@ -23548,10 +23548,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D73" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E73" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F73" t="n">
         <v>44.50312779267203</v>
@@ -23575,10 +23575,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D74" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E74" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F74" t="n">
         <v>44.50312779267203</v>
@@ -23602,10 +23602,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D75" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E75" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F75" t="n">
         <v>44.50312779267203</v>
@@ -23629,10 +23629,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D76" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E76" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F76" t="n">
         <v>44.50312779267203</v>
@@ -23656,10 +23656,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D77" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E77" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F77" t="n">
         <v>44.50312779267203</v>
@@ -23683,10 +23683,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D78" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E78" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F78" t="n">
         <v>44.50312779267203</v>
@@ -23710,10 +23710,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D79" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E79" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F79" t="n">
         <v>44.50312779267203</v>
@@ -23737,10 +23737,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D80" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E80" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F80" t="n">
         <v>44.50312779267203</v>
@@ -23764,10 +23764,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D81" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E81" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F81" t="n">
         <v>44.50312779267203</v>
@@ -24382,16 +24382,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D6" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E6" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F6" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G6" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="7">
@@ -24409,16 +24409,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D7" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E7" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F7" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G7" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="8">
@@ -24436,16 +24436,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D8" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E8" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F8" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G8" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="9">
@@ -24463,16 +24463,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D9" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E9" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F9" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G9" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="10">
@@ -24490,16 +24490,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D10" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E10" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F10" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G10" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="11">
@@ -24517,16 +24517,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D11" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E11" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F11" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G11" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="12">
@@ -24544,16 +24544,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D12" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E12" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F12" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G12" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="13">
@@ -24571,16 +24571,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D13" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E13" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F13" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G13" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="14">
@@ -24598,16 +24598,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D14" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E14" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F14" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G14" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="15">
@@ -24625,16 +24625,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D15" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E15" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F15" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G15" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="16">
@@ -24652,16 +24652,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D16" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E16" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F16" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G16" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="17">
@@ -24679,16 +24679,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D17" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E17" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F17" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G17" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="18">
@@ -24706,16 +24706,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D18" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E18" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F18" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G18" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="19">
@@ -24733,16 +24733,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D19" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E19" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F19" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G19" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="20">
@@ -24760,16 +24760,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D20" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E20" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F20" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G20" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="21">
@@ -24787,16 +24787,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D21" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E21" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F21" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G21" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="22">
@@ -24814,16 +24814,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D22" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E22" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F22" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G22" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="23">
@@ -24841,16 +24841,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D23" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E23" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F23" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G23" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="24">
@@ -24868,16 +24868,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D24" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E24" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F24" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G24" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="25">
@@ -24895,16 +24895,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D25" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E25" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F25" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G25" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="26">
@@ -24931,7 +24931,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G26" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="27">
@@ -24958,7 +24958,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G27" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="28">
@@ -24985,7 +24985,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G28" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="29">
@@ -25012,7 +25012,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G29" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="30">
@@ -25039,7 +25039,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G30" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="31">
@@ -25066,7 +25066,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G31" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="32">
@@ -25093,7 +25093,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G32" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="33">
@@ -25120,7 +25120,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G33" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="34">
@@ -25147,7 +25147,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G34" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="35">
@@ -25174,7 +25174,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G35" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="36">
@@ -25201,7 +25201,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G36" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="37">
@@ -25228,7 +25228,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G37" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="38">
@@ -25255,7 +25255,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G38" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="39">
@@ -25282,7 +25282,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G39" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="40">
@@ -25309,7 +25309,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G40" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="41">
@@ -25336,7 +25336,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G41" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="42">
@@ -28762,7 +28762,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G70" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="71">
@@ -28789,7 +28789,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G71" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="72">
@@ -28816,7 +28816,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G72" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="73">
@@ -28843,7 +28843,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G73" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="74">
@@ -28870,7 +28870,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G74" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="75">
@@ -28897,7 +28897,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G75" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="76">
@@ -28924,7 +28924,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G76" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="77">
@@ -28951,7 +28951,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G77" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="78">
@@ -28978,7 +28978,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G78" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="79">
@@ -29005,7 +29005,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G79" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="80">
@@ -29032,7 +29032,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G80" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="81">
@@ -29059,7 +29059,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G81" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="82">
@@ -29569,7 +29569,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G2" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="3">
@@ -29596,7 +29596,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G3" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="4">
@@ -29623,7 +29623,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G4" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="5">
@@ -29650,7 +29650,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G5" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="6">
@@ -30649,7 +30649,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G42" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="43">
@@ -30676,7 +30676,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G43" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="44">
@@ -30703,7 +30703,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G44" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="45">
@@ -30730,7 +30730,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G45" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="46">
@@ -30757,7 +30757,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G46" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="47">
@@ -30784,7 +30784,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G47" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="48">
@@ -30811,7 +30811,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G48" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="49">
@@ -30838,7 +30838,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G49" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="50">
@@ -30865,7 +30865,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G50" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="51">
@@ -30892,7 +30892,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G51" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="52">
@@ -30919,7 +30919,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G52" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="53">
@@ -30946,7 +30946,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G53" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="54">
@@ -30973,7 +30973,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="55">
@@ -31000,7 +31000,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G55" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="56">
@@ -31027,7 +31027,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G56" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="57">
@@ -31054,7 +31054,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G57" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="58">
@@ -31081,7 +31081,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G58" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="59">
@@ -31108,7 +31108,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G59" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="60">
@@ -31135,7 +31135,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G60" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="61">
@@ -31162,7 +31162,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G61" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="62">
@@ -31189,7 +31189,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G62" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="63">
@@ -31216,7 +31216,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G63" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="64">
@@ -31243,7 +31243,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G64" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="65">
@@ -31270,7 +31270,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G65" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="66">
@@ -31297,7 +31297,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G66" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="67">
@@ -31324,7 +31324,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="68">
@@ -31351,7 +31351,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G68" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="69">
@@ -31378,7 +31378,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G69" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="70">
@@ -36691,7 +36691,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G70" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="71">
@@ -36718,7 +36718,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G71" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="72">
@@ -36745,7 +36745,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G72" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="73">
@@ -36772,7 +36772,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G73" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="74">
@@ -36799,7 +36799,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G74" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="75">
@@ -36826,7 +36826,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G75" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="76">
@@ -36853,7 +36853,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G76" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="77">
@@ -36880,7 +36880,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G77" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="78">
@@ -36907,7 +36907,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G78" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="79">
@@ -36934,7 +36934,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G79" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="80">
@@ -36961,7 +36961,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G80" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="81">
@@ -36988,7 +36988,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G81" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="82">
@@ -37498,7 +37498,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G2" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="3">
@@ -37525,7 +37525,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G3" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="4">
@@ -37552,7 +37552,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G4" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="5">
@@ -37579,7 +37579,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G5" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="6">
@@ -38578,7 +38578,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G42" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="43">
@@ -38605,7 +38605,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G43" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="44">
@@ -38632,7 +38632,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G44" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="45">
@@ -38659,7 +38659,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G45" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="46">
@@ -38686,7 +38686,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G46" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="47">
@@ -38713,7 +38713,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G47" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="48">
@@ -38740,7 +38740,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G48" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="49">
@@ -38767,7 +38767,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G49" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="50">
@@ -38794,7 +38794,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G50" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="51">
@@ -38821,7 +38821,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G51" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="52">
@@ -38848,7 +38848,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G52" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="53">
@@ -38875,7 +38875,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G53" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="54">
@@ -38902,7 +38902,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G54" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="55">
@@ -38929,7 +38929,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G55" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="56">
@@ -38956,7 +38956,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G56" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="57">
@@ -38983,7 +38983,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G57" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="58">
@@ -39010,7 +39010,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G58" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="59">
@@ -39037,7 +39037,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G59" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="60">
@@ -39064,7 +39064,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G60" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="61">
@@ -39091,7 +39091,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G61" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="62">
@@ -39118,7 +39118,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G62" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="63">
@@ -39145,7 +39145,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G63" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="64">
@@ -39172,7 +39172,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G64" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="65">
@@ -39199,7 +39199,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G65" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="66">
@@ -39226,7 +39226,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G66" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="67">
@@ -39253,7 +39253,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G67" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="68">
@@ -39280,7 +39280,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G68" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="69">
@@ -39307,7 +39307,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G69" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="70">
@@ -41965,7 +41965,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D70" t="n">
         <v>24.43126133466969</v>
@@ -41974,7 +41974,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F70" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G70" t="n">
         <v>2.05868133214936</v>
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D71" t="n">
         <v>24.43126133466969</v>
@@ -42001,7 +42001,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F71" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G71" t="n">
         <v>2.05868133214936</v>
@@ -42019,7 +42019,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D72" t="n">
         <v>24.43126133466969</v>
@@ -42028,7 +42028,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F72" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G72" t="n">
         <v>2.05868133214936</v>
@@ -42046,7 +42046,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D73" t="n">
         <v>24.43126133466969</v>
@@ -42055,7 +42055,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F73" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G73" t="n">
         <v>2.05868133214936</v>
@@ -42073,7 +42073,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D74" t="n">
         <v>24.43126133466969</v>
@@ -42082,7 +42082,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F74" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G74" t="n">
         <v>2.05868133214936</v>
@@ -42100,7 +42100,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D75" t="n">
         <v>24.43126133466969</v>
@@ -42109,7 +42109,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F75" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G75" t="n">
         <v>2.05868133214936</v>
@@ -42127,7 +42127,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D76" t="n">
         <v>24.43126133466969</v>
@@ -42136,7 +42136,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F76" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G76" t="n">
         <v>2.05868133214936</v>
@@ -42154,7 +42154,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D77" t="n">
         <v>24.43126133466969</v>
@@ -42163,7 +42163,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F77" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G77" t="n">
         <v>2.05868133214936</v>
@@ -42181,7 +42181,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D78" t="n">
         <v>24.43126133466969</v>
@@ -42190,7 +42190,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F78" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G78" t="n">
         <v>2.05868133214936</v>
@@ -42208,7 +42208,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D79" t="n">
         <v>24.43126133466969</v>
@@ -42217,7 +42217,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F79" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G79" t="n">
         <v>2.05868133214936</v>
@@ -42235,7 +42235,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D80" t="n">
         <v>24.43126133466969</v>
@@ -42244,7 +42244,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F80" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G80" t="n">
         <v>2.05868133214936</v>
@@ -42262,7 +42262,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D81" t="n">
         <v>24.43126133466969</v>
@@ -42271,7 +42271,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F81" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G81" t="n">
         <v>2.05868133214936</v>
@@ -48706,7 +48706,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D26" t="n">
         <v>19.28759329767769</v>
@@ -48715,7 +48715,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F26" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G26" t="n">
         <v>11.57427084076214</v>
@@ -48733,7 +48733,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D27" t="n">
         <v>19.28759329767769</v>
@@ -48742,7 +48742,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F27" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G27" t="n">
         <v>11.57427084076214</v>
@@ -48760,7 +48760,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D28" t="n">
         <v>19.28759329767769</v>
@@ -48769,7 +48769,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F28" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G28" t="n">
         <v>11.57427084076214</v>
@@ -48787,7 +48787,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D29" t="n">
         <v>19.28759329767769</v>
@@ -48796,7 +48796,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F29" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G29" t="n">
         <v>11.57427084076214</v>
@@ -48814,7 +48814,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D30" t="n">
         <v>19.28759329767769</v>
@@ -48823,7 +48823,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F30" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G30" t="n">
         <v>11.57427084076214</v>
@@ -48841,7 +48841,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D31" t="n">
         <v>19.28759329767769</v>
@@ -48850,7 +48850,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F31" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G31" t="n">
         <v>11.57427084076214</v>
@@ -48868,7 +48868,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D32" t="n">
         <v>19.28759329767769</v>
@@ -48877,7 +48877,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F32" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G32" t="n">
         <v>11.57427084076214</v>
@@ -48895,7 +48895,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D33" t="n">
         <v>19.28759329767769</v>
@@ -48904,7 +48904,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F33" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G33" t="n">
         <v>11.57427084076214</v>
@@ -48922,7 +48922,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D34" t="n">
         <v>19.28759329767769</v>
@@ -48931,7 +48931,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F34" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G34" t="n">
         <v>11.57427084076214</v>
@@ -48949,7 +48949,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D35" t="n">
         <v>19.28759329767769</v>
@@ -48958,7 +48958,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F35" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G35" t="n">
         <v>11.57427084076214</v>
@@ -48976,7 +48976,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D36" t="n">
         <v>19.28759329767769</v>
@@ -48985,7 +48985,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F36" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G36" t="n">
         <v>11.57427084076214</v>
@@ -49003,7 +49003,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D37" t="n">
         <v>19.28759329767769</v>
@@ -49012,7 +49012,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F37" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G37" t="n">
         <v>11.57427084076214</v>
@@ -49030,7 +49030,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D38" t="n">
         <v>19.28759329767769</v>
@@ -49039,7 +49039,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F38" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G38" t="n">
         <v>11.57427084076214</v>
@@ -49057,7 +49057,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D39" t="n">
         <v>19.28759329767769</v>
@@ -49066,7 +49066,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F39" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G39" t="n">
         <v>11.57427084076214</v>
@@ -49084,7 +49084,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D40" t="n">
         <v>19.28759329767769</v>
@@ -49093,7 +49093,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F40" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G40" t="n">
         <v>11.57427084076214</v>
@@ -49111,7 +49111,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D41" t="n">
         <v>19.28759329767769</v>
@@ -49120,7 +49120,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F41" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G41" t="n">
         <v>11.57427084076214</v>
@@ -50230,7 +50230,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G82" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="83">
@@ -50257,7 +50257,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G83" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="84">
@@ -50284,7 +50284,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G84" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="85">
@@ -50311,7 +50311,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G85" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="86">
@@ -50338,7 +50338,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G86" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="87">
@@ -50365,7 +50365,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G87" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="88">
@@ -50392,7 +50392,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G88" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="89">
@@ -50419,7 +50419,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G89" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="90">
@@ -50446,7 +50446,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G90" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="91">
@@ -50473,7 +50473,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G91" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="92">
@@ -50500,7 +50500,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G92" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="93">
@@ -50527,7 +50527,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G93" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="94">
@@ -50554,7 +50554,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G94" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="95">
@@ -50581,7 +50581,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G95" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="96">
@@ -50608,7 +50608,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G96" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="97">
@@ -50635,7 +50635,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G97" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Combined_sheet_output_speed/GA/GA_2030_ABM.xlsx
+++ b/backend/Combined_sheet_output_speed/GA/GA_2030_ABM.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="tract=13121001001" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tract=13121001002" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tract=13121001201" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="tract=13121001202" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="tract=13121001800" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="tract=13121001900" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="tract=13121002100" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="tract=13121002600" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="tract=13121002800" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="tract=13121003500" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="tract=13121003600" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="tract=13121003800" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="tract=13121004300" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="tract=13121004400" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="tract=13121004800" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="tract=13121004900" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="tract=13121005800" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="tract=13121011800" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="tract=13121011900" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="tract=13121012000" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001002" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001201" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001202" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001800" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001900" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121002100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121002600" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121002800" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121003500" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121003600" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121003800" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004300" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004400" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004800" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004900" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121005800" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121011800" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121011900" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121012000" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3787,7 +3787,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G26" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="27">
@@ -3814,7 +3814,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G27" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="28">
@@ -3841,7 +3841,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G28" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="29">
@@ -3868,7 +3868,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G29" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="30">
@@ -3895,7 +3895,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G30" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="31">
@@ -3922,7 +3922,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G31" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="32">
@@ -3949,7 +3949,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G32" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="33">
@@ -3976,7 +3976,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G33" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="34">
@@ -4003,7 +4003,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G34" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="35">
@@ -4030,7 +4030,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G35" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="36">
@@ -4057,7 +4057,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G36" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="37">
@@ -4084,7 +4084,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G37" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="38">
@@ -4111,7 +4111,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G38" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="39">
@@ -4138,7 +4138,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G39" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="40">
@@ -4165,7 +4165,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G40" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="41">
@@ -4192,7 +4192,7 @@
         <v>312.3120740019474</v>
       </c>
       <c r="G41" t="n">
-        <v>17.05399235679811</v>
+        <v>17.0539923567981</v>
       </c>
     </row>
     <row r="42">
@@ -5290,10 +5290,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D82" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E82" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F82" t="n">
         <v>270.7395326192794</v>
@@ -5317,10 +5317,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D83" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E83" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F83" t="n">
         <v>270.7395326192794</v>
@@ -5344,10 +5344,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D84" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E84" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F84" t="n">
         <v>270.7395326192794</v>
@@ -5371,10 +5371,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D85" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E85" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F85" t="n">
         <v>270.7395326192794</v>
@@ -5398,10 +5398,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D86" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E86" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F86" t="n">
         <v>270.7395326192794</v>
@@ -5425,10 +5425,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D87" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E87" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F87" t="n">
         <v>270.7395326192794</v>
@@ -5452,10 +5452,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D88" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E88" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F88" t="n">
         <v>270.7395326192794</v>
@@ -5479,10 +5479,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D89" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E89" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F89" t="n">
         <v>270.7395326192794</v>
@@ -5506,10 +5506,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D90" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E90" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F90" t="n">
         <v>270.7395326192794</v>
@@ -5533,10 +5533,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D91" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E91" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F91" t="n">
         <v>270.7395326192794</v>
@@ -5560,10 +5560,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D92" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E92" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F92" t="n">
         <v>270.7395326192794</v>
@@ -5587,10 +5587,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D93" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E93" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F93" t="n">
         <v>270.7395326192794</v>
@@ -5614,10 +5614,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D94" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E94" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F94" t="n">
         <v>270.7395326192794</v>
@@ -5641,10 +5641,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D95" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E95" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F95" t="n">
         <v>270.7395326192794</v>
@@ -5668,10 +5668,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D96" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E96" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F96" t="n">
         <v>270.7395326192794</v>
@@ -5695,10 +5695,10 @@
         <v>270.7395326192794</v>
       </c>
       <c r="D97" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="E97" t="n">
-        <v>19.3673406972499</v>
+        <v>19.36734069724989</v>
       </c>
       <c r="F97" t="n">
         <v>270.7395326192794</v>
@@ -7933,16 +7933,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D82" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E82" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F82" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G82" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="83">
@@ -7960,16 +7960,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D83" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E83" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F83" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G83" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="84">
@@ -7987,16 +7987,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D84" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E84" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F84" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G84" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="85">
@@ -8014,16 +8014,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D85" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E85" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F85" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G85" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="86">
@@ -8041,16 +8041,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D86" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E86" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F86" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G86" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="87">
@@ -8068,16 +8068,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D87" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E87" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F87" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G87" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="88">
@@ -8095,16 +8095,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D88" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E88" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F88" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G88" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="89">
@@ -8122,16 +8122,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D89" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E89" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F89" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G89" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="90">
@@ -8149,16 +8149,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D90" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E90" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F90" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G90" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="91">
@@ -8176,16 +8176,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D91" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E91" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F91" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G91" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="92">
@@ -8203,16 +8203,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D92" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E92" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F92" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G92" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="93">
@@ -8230,16 +8230,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D93" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E93" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F93" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G93" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="94">
@@ -8257,16 +8257,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D94" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E94" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F94" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G94" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="95">
@@ -8284,16 +8284,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D95" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E95" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F95" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G95" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="96">
@@ -8311,16 +8311,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D96" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E96" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F96" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G96" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
     <row r="97">
@@ -8338,16 +8338,16 @@
         <v>119.525406504065</v>
       </c>
       <c r="D97" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="E97" t="n">
-        <v>19.00339080168175</v>
+        <v>19.00339080168176</v>
       </c>
       <c r="F97" t="n">
         <v>119.525406504065</v>
       </c>
       <c r="G97" t="n">
-        <v>6.289688390425952</v>
+        <v>6.289688390425951</v>
       </c>
     </row>
   </sheetData>
@@ -9073,7 +9073,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G26" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="27">
@@ -9100,7 +9100,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G27" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="28">
@@ -9127,7 +9127,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G28" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="29">
@@ -9154,7 +9154,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G29" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="30">
@@ -9181,7 +9181,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G30" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="31">
@@ -9208,7 +9208,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G31" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="32">
@@ -9235,7 +9235,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G32" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="33">
@@ -9262,7 +9262,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G33" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="34">
@@ -9289,7 +9289,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G34" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="35">
@@ -9316,7 +9316,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G35" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="36">
@@ -9343,7 +9343,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G36" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="37">
@@ -9370,7 +9370,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G37" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="38">
@@ -9397,7 +9397,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G38" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="39">
@@ -9424,7 +9424,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G39" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="40">
@@ -9451,7 +9451,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G40" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="41">
@@ -9478,7 +9478,7 @@
         <v>122.8112416107382</v>
       </c>
       <c r="G41" t="n">
-        <v>5.707028101644244</v>
+        <v>5.707028101644243</v>
       </c>
     </row>
     <row r="42">
@@ -15871,7 +15871,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G82" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="83">
@@ -15898,7 +15898,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G83" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="84">
@@ -15925,7 +15925,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G84" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="85">
@@ -15952,7 +15952,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G85" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="86">
@@ -15979,7 +15979,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G86" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="87">
@@ -16006,7 +16006,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G87" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="88">
@@ -16033,7 +16033,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G88" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="89">
@@ -16060,7 +16060,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G89" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="90">
@@ -16087,7 +16087,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G90" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G91" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="92">
@@ -16141,7 +16141,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G92" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="93">
@@ -16168,7 +16168,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G93" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="94">
@@ -16195,7 +16195,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G94" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="95">
@@ -16222,7 +16222,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G95" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="96">
@@ -16249,7 +16249,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G96" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
     <row r="97">
@@ -16276,7 +16276,7 @@
         <v>331.5390625</v>
       </c>
       <c r="G97" t="n">
-        <v>11.91214920106023</v>
+        <v>11.91214920106024</v>
       </c>
     </row>
   </sheetData>
@@ -18505,10 +18505,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D82" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E82" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F82" t="n">
         <v>429.3168316831683</v>
@@ -18532,10 +18532,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D83" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E83" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F83" t="n">
         <v>429.3168316831683</v>
@@ -18559,10 +18559,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D84" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E84" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F84" t="n">
         <v>429.3168316831683</v>
@@ -18586,10 +18586,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D85" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E85" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F85" t="n">
         <v>429.3168316831683</v>
@@ -18613,10 +18613,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D86" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E86" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F86" t="n">
         <v>429.3168316831683</v>
@@ -18640,10 +18640,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D87" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E87" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F87" t="n">
         <v>429.3168316831683</v>
@@ -18667,10 +18667,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D88" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E88" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F88" t="n">
         <v>429.3168316831683</v>
@@ -18694,10 +18694,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D89" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E89" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F89" t="n">
         <v>429.3168316831683</v>
@@ -18721,10 +18721,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D90" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E90" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F90" t="n">
         <v>429.3168316831683</v>
@@ -18748,10 +18748,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D91" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E91" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F91" t="n">
         <v>429.3168316831683</v>
@@ -18775,10 +18775,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D92" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E92" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F92" t="n">
         <v>429.3168316831683</v>
@@ -18802,10 +18802,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D93" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E93" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F93" t="n">
         <v>429.3168316831683</v>
@@ -18829,10 +18829,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D94" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E94" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F94" t="n">
         <v>429.3168316831683</v>
@@ -18856,10 +18856,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D95" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E95" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F95" t="n">
         <v>429.3168316831683</v>
@@ -18883,10 +18883,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D96" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E96" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F96" t="n">
         <v>429.3168316831683</v>
@@ -18910,10 +18910,10 @@
         <v>429.3168316831683</v>
       </c>
       <c r="D97" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="E97" t="n">
-        <v>27.71778063508062</v>
+        <v>27.71778063508061</v>
       </c>
       <c r="F97" t="n">
         <v>429.3168316831683</v>
@@ -19096,10 +19096,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D6" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E6" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F6" t="n">
         <v>303.494623655914</v>
@@ -19123,10 +19123,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D7" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E7" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F7" t="n">
         <v>303.494623655914</v>
@@ -19150,10 +19150,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D8" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E8" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F8" t="n">
         <v>303.494623655914</v>
@@ -19177,10 +19177,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D9" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E9" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F9" t="n">
         <v>303.494623655914</v>
@@ -19204,10 +19204,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D10" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E10" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F10" t="n">
         <v>303.494623655914</v>
@@ -19231,10 +19231,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D11" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E11" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F11" t="n">
         <v>303.494623655914</v>
@@ -19258,10 +19258,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D12" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E12" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F12" t="n">
         <v>303.494623655914</v>
@@ -19285,10 +19285,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D13" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E13" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F13" t="n">
         <v>303.494623655914</v>
@@ -19312,10 +19312,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D14" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E14" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F14" t="n">
         <v>303.494623655914</v>
@@ -19339,10 +19339,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D15" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E15" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F15" t="n">
         <v>303.494623655914</v>
@@ -19366,10 +19366,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D16" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E16" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F16" t="n">
         <v>303.494623655914</v>
@@ -19393,10 +19393,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D17" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E17" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F17" t="n">
         <v>303.494623655914</v>
@@ -19420,10 +19420,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D18" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E18" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F18" t="n">
         <v>303.494623655914</v>
@@ -19447,10 +19447,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D19" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E19" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F19" t="n">
         <v>303.494623655914</v>
@@ -19474,10 +19474,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D20" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E20" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F20" t="n">
         <v>303.494623655914</v>
@@ -19501,10 +19501,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D21" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E21" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F21" t="n">
         <v>303.494623655914</v>
@@ -19528,10 +19528,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D22" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E22" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F22" t="n">
         <v>303.494623655914</v>
@@ -19555,10 +19555,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D23" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E23" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F23" t="n">
         <v>303.494623655914</v>
@@ -19582,10 +19582,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D24" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E24" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F24" t="n">
         <v>303.494623655914</v>
@@ -19609,10 +19609,10 @@
         <v>303.494623655914</v>
       </c>
       <c r="D25" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="E25" t="n">
-        <v>24.99416768941894</v>
+        <v>24.99416768941893</v>
       </c>
       <c r="F25" t="n">
         <v>303.494623655914</v>
@@ -21148,10 +21148,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D82" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E82" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F82" t="n">
         <v>382.3458781362007</v>
@@ -21175,10 +21175,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D83" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E83" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F83" t="n">
         <v>382.3458781362007</v>
@@ -21202,10 +21202,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D84" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E84" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F84" t="n">
         <v>382.3458781362007</v>
@@ -21229,10 +21229,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D85" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E85" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F85" t="n">
         <v>382.3458781362007</v>
@@ -21256,10 +21256,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D86" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E86" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F86" t="n">
         <v>382.3458781362007</v>
@@ -21283,10 +21283,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D87" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E87" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F87" t="n">
         <v>382.3458781362007</v>
@@ -21310,10 +21310,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D88" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E88" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F88" t="n">
         <v>382.3458781362007</v>
@@ -21337,10 +21337,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D89" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E89" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F89" t="n">
         <v>382.3458781362007</v>
@@ -21364,10 +21364,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D90" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E90" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F90" t="n">
         <v>382.3458781362007</v>
@@ -21391,10 +21391,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D91" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E91" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F91" t="n">
         <v>382.3458781362007</v>
@@ -21418,10 +21418,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D92" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E92" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F92" t="n">
         <v>382.3458781362007</v>
@@ -21445,10 +21445,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D93" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E93" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F93" t="n">
         <v>382.3458781362007</v>
@@ -21472,10 +21472,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D94" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E94" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F94" t="n">
         <v>382.3458781362007</v>
@@ -21499,10 +21499,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D95" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E95" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F95" t="n">
         <v>382.3458781362007</v>
@@ -21526,10 +21526,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D96" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E96" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F96" t="n">
         <v>382.3458781362007</v>
@@ -21553,10 +21553,10 @@
         <v>382.3458781362007</v>
       </c>
       <c r="D97" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="E97" t="n">
-        <v>23.21818567718399</v>
+        <v>23.218185677184</v>
       </c>
       <c r="F97" t="n">
         <v>382.3458781362007</v>
@@ -21748,7 +21748,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G6" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="7">
@@ -21775,7 +21775,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G7" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="8">
@@ -21802,7 +21802,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G8" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="9">
@@ -21829,7 +21829,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G9" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="10">
@@ -21856,7 +21856,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G10" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="11">
@@ -21883,7 +21883,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G11" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="12">
@@ -21910,7 +21910,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G12" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="13">
@@ -21937,7 +21937,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G13" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="14">
@@ -21964,7 +21964,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G14" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="15">
@@ -21991,7 +21991,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G15" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="16">
@@ -22018,7 +22018,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G16" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="17">
@@ -22045,7 +22045,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G17" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="18">
@@ -22072,7 +22072,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G18" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="19">
@@ -22099,7 +22099,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G19" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="20">
@@ -22126,7 +22126,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G20" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="21">
@@ -22153,7 +22153,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G21" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="22">
@@ -22180,7 +22180,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G22" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="23">
@@ -22207,7 +22207,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G23" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="24">
@@ -22234,7 +22234,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G24" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="25">
@@ -22261,7 +22261,7 @@
         <v>182.4445040214477</v>
       </c>
       <c r="G25" t="n">
-        <v>6.492070512260168</v>
+        <v>6.492070512260167</v>
       </c>
     </row>
     <row r="26">
@@ -23467,10 +23467,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D70" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E70" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F70" t="n">
         <v>44.50312779267203</v>
@@ -23494,10 +23494,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D71" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E71" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F71" t="n">
         <v>44.50312779267203</v>
@@ -23521,10 +23521,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D72" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E72" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F72" t="n">
         <v>44.50312779267203</v>
@@ -23548,10 +23548,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D73" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E73" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F73" t="n">
         <v>44.50312779267203</v>
@@ -23575,10 +23575,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D74" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E74" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F74" t="n">
         <v>44.50312779267203</v>
@@ -23602,10 +23602,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D75" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E75" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F75" t="n">
         <v>44.50312779267203</v>
@@ -23629,10 +23629,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D76" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E76" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F76" t="n">
         <v>44.50312779267203</v>
@@ -23656,10 +23656,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D77" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E77" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F77" t="n">
         <v>44.50312779267203</v>
@@ -23683,10 +23683,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D78" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E78" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F78" t="n">
         <v>44.50312779267203</v>
@@ -23710,10 +23710,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D79" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E79" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F79" t="n">
         <v>44.50312779267203</v>
@@ -23737,10 +23737,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D80" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E80" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F80" t="n">
         <v>44.50312779267203</v>
@@ -23764,10 +23764,10 @@
         <v>44.50312779267203</v>
       </c>
       <c r="D81" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="E81" t="n">
-        <v>28.64413276444074</v>
+        <v>28.64413276444073</v>
       </c>
       <c r="F81" t="n">
         <v>44.50312779267203</v>
@@ -24382,16 +24382,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D6" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E6" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F6" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G6" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="7">
@@ -24409,16 +24409,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D7" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E7" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F7" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G7" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="8">
@@ -24436,16 +24436,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D8" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E8" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F8" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G8" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="9">
@@ -24463,16 +24463,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D9" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E9" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F9" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G9" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="10">
@@ -24490,16 +24490,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D10" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E10" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F10" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G10" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="11">
@@ -24517,16 +24517,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D11" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E11" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F11" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G11" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="12">
@@ -24544,16 +24544,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D12" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E12" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F12" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G12" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="13">
@@ -24571,16 +24571,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D13" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E13" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F13" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G13" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="14">
@@ -24598,16 +24598,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D14" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E14" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F14" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G14" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="15">
@@ -24625,16 +24625,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D15" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E15" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F15" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G15" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="16">
@@ -24652,16 +24652,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D16" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E16" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F16" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G16" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="17">
@@ -24679,16 +24679,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D17" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E17" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F17" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G17" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="18">
@@ -24706,16 +24706,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D18" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E18" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F18" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G18" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="19">
@@ -24733,16 +24733,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D19" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E19" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F19" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G19" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="20">
@@ -24760,16 +24760,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D20" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E20" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F20" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G20" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="21">
@@ -24787,16 +24787,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D21" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E21" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F21" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G21" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="22">
@@ -24814,16 +24814,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D22" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E22" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F22" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G22" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="23">
@@ -24841,16 +24841,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D23" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E23" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F23" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G23" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="24">
@@ -24868,16 +24868,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D24" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E24" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F24" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G24" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="25">
@@ -24895,16 +24895,16 @@
         <v>157.7790849673203</v>
       </c>
       <c r="D25" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="E25" t="n">
-        <v>23.31612219745887</v>
+        <v>23.31612219745888</v>
       </c>
       <c r="F25" t="n">
         <v>157.7790849673203</v>
       </c>
       <c r="G25" t="n">
-        <v>6.76695222435041</v>
+        <v>6.766952224350408</v>
       </c>
     </row>
     <row r="26">
@@ -24931,7 +24931,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G26" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="27">
@@ -24958,7 +24958,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G27" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="28">
@@ -24985,7 +24985,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G28" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="29">
@@ -25012,7 +25012,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G29" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="30">
@@ -25039,7 +25039,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G30" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="31">
@@ -25066,7 +25066,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G31" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="32">
@@ -25093,7 +25093,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G32" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="33">
@@ -25120,7 +25120,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G33" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="34">
@@ -25147,7 +25147,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G34" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="35">
@@ -25174,7 +25174,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G35" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="36">
@@ -25201,7 +25201,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G36" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="37">
@@ -25228,7 +25228,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G37" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="38">
@@ -25255,7 +25255,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G38" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="39">
@@ -25282,7 +25282,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G39" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="40">
@@ -25309,7 +25309,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G40" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="41">
@@ -25336,7 +25336,7 @@
         <v>229.734068627451</v>
       </c>
       <c r="G41" t="n">
-        <v>10.35006021669049</v>
+        <v>10.35006021669048</v>
       </c>
     </row>
     <row r="42">
@@ -28762,7 +28762,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G70" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="71">
@@ -28789,7 +28789,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G71" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="72">
@@ -28816,7 +28816,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G72" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="73">
@@ -28843,7 +28843,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G73" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="74">
@@ -28870,7 +28870,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G74" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="75">
@@ -28897,7 +28897,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G75" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="76">
@@ -28924,7 +28924,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G76" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="77">
@@ -28951,7 +28951,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G77" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="78">
@@ -28978,7 +28978,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G78" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="79">
@@ -29005,7 +29005,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G79" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="80">
@@ -29032,7 +29032,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G80" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="81">
@@ -29059,7 +29059,7 @@
         <v>73.19194823867721</v>
       </c>
       <c r="G81" t="n">
-        <v>3.217229394591522</v>
+        <v>3.217229394591521</v>
       </c>
     </row>
     <row r="82">
@@ -29569,7 +29569,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G2" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="3">
@@ -29596,7 +29596,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G3" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="4">
@@ -29623,7 +29623,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G4" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="5">
@@ -29650,7 +29650,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G5" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="6">
@@ -30649,7 +30649,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G42" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="43">
@@ -30676,7 +30676,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G43" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="44">
@@ -30703,7 +30703,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G44" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="45">
@@ -30730,7 +30730,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G45" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="46">
@@ -30757,7 +30757,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G46" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="47">
@@ -30784,7 +30784,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G47" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="48">
@@ -30811,7 +30811,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G48" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="49">
@@ -30838,7 +30838,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G49" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="50">
@@ -30865,7 +30865,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G50" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="51">
@@ -30892,7 +30892,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G51" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="52">
@@ -30919,7 +30919,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G52" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="53">
@@ -30946,7 +30946,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G53" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="54">
@@ -30973,7 +30973,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="55">
@@ -31000,7 +31000,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G55" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="56">
@@ -31027,7 +31027,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G56" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="57">
@@ -31054,7 +31054,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G57" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="58">
@@ -31081,7 +31081,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G58" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="59">
@@ -31108,7 +31108,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G59" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="60">
@@ -31135,7 +31135,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G60" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="61">
@@ -31162,7 +31162,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G61" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="62">
@@ -31189,7 +31189,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G62" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="63">
@@ -31216,7 +31216,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G63" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="64">
@@ -31243,7 +31243,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G64" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="65">
@@ -31270,7 +31270,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G65" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="66">
@@ -31297,7 +31297,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G66" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="67">
@@ -31324,7 +31324,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G67" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="68">
@@ -31351,7 +31351,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G68" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="69">
@@ -31378,7 +31378,7 @@
         <v>77.35511363636364</v>
       </c>
       <c r="G69" t="n">
-        <v>3.94327571911583</v>
+        <v>3.943275719115829</v>
       </c>
     </row>
     <row r="70">
@@ -36691,7 +36691,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G70" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="71">
@@ -36718,7 +36718,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G71" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="72">
@@ -36745,7 +36745,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G72" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="73">
@@ -36772,7 +36772,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G73" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="74">
@@ -36799,7 +36799,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G74" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="75">
@@ -36826,7 +36826,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G75" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="76">
@@ -36853,7 +36853,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G76" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="77">
@@ -36880,7 +36880,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G77" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="78">
@@ -36907,7 +36907,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G78" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="79">
@@ -36934,7 +36934,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G79" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="80">
@@ -36961,7 +36961,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G80" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="81">
@@ -36988,7 +36988,7 @@
         <v>21.21617161716172</v>
       </c>
       <c r="G81" t="n">
-        <v>1.032803189430869</v>
+        <v>1.03280318943087</v>
       </c>
     </row>
     <row r="82">
@@ -37498,7 +37498,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G2" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="3">
@@ -37525,7 +37525,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G3" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="4">
@@ -37552,7 +37552,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G4" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="5">
@@ -37579,7 +37579,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G5" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="6">
@@ -38578,7 +38578,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G42" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="43">
@@ -38605,7 +38605,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G43" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="44">
@@ -38632,7 +38632,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G44" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="45">
@@ -38659,7 +38659,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G45" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="46">
@@ -38686,7 +38686,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G46" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="47">
@@ -38713,7 +38713,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G47" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="48">
@@ -38740,7 +38740,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G48" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="49">
@@ -38767,7 +38767,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G49" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="50">
@@ -38794,7 +38794,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G50" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="51">
@@ -38821,7 +38821,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G51" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="52">
@@ -38848,7 +38848,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G52" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="53">
@@ -38875,7 +38875,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G53" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="54">
@@ -38902,7 +38902,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G54" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="55">
@@ -38929,7 +38929,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G55" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="56">
@@ -38956,7 +38956,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G56" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="57">
@@ -38983,7 +38983,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G57" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="58">
@@ -39010,7 +39010,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G58" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="59">
@@ -39037,7 +39037,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G59" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="60">
@@ -39064,7 +39064,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G60" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="61">
@@ -39091,7 +39091,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G61" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="62">
@@ -39118,7 +39118,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G62" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="63">
@@ -39145,7 +39145,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G63" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="64">
@@ -39172,7 +39172,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G64" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="65">
@@ -39199,7 +39199,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G65" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="66">
@@ -39226,7 +39226,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G66" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="67">
@@ -39253,7 +39253,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G67" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="68">
@@ -39280,7 +39280,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G68" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="69">
@@ -39307,7 +39307,7 @@
         <v>50.77236842105263</v>
       </c>
       <c r="G69" t="n">
-        <v>2.618912029875758</v>
+        <v>2.618912029875757</v>
       </c>
     </row>
     <row r="70">
@@ -41965,7 +41965,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D70" t="n">
         <v>24.43126133466969</v>
@@ -41974,7 +41974,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F70" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G70" t="n">
         <v>2.05868133214936</v>
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D71" t="n">
         <v>24.43126133466969</v>
@@ -42001,7 +42001,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F71" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G71" t="n">
         <v>2.05868133214936</v>
@@ -42019,7 +42019,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D72" t="n">
         <v>24.43126133466969</v>
@@ -42028,7 +42028,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F72" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G72" t="n">
         <v>2.05868133214936</v>
@@ -42046,7 +42046,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D73" t="n">
         <v>24.43126133466969</v>
@@ -42055,7 +42055,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F73" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G73" t="n">
         <v>2.05868133214936</v>
@@ -42073,7 +42073,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D74" t="n">
         <v>24.43126133466969</v>
@@ -42082,7 +42082,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F74" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G74" t="n">
         <v>2.05868133214936</v>
@@ -42100,7 +42100,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D75" t="n">
         <v>24.43126133466969</v>
@@ -42109,7 +42109,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F75" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G75" t="n">
         <v>2.05868133214936</v>
@@ -42127,7 +42127,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D76" t="n">
         <v>24.43126133466969</v>
@@ -42136,7 +42136,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F76" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G76" t="n">
         <v>2.05868133214936</v>
@@ -42154,7 +42154,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D77" t="n">
         <v>24.43126133466969</v>
@@ -42163,7 +42163,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F77" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G77" t="n">
         <v>2.05868133214936</v>
@@ -42181,7 +42181,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D78" t="n">
         <v>24.43126133466969</v>
@@ -42190,7 +42190,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F78" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G78" t="n">
         <v>2.05868133214936</v>
@@ -42208,7 +42208,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D79" t="n">
         <v>24.43126133466969</v>
@@ -42217,7 +42217,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F79" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G79" t="n">
         <v>2.05868133214936</v>
@@ -42235,7 +42235,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D80" t="n">
         <v>24.43126133466969</v>
@@ -42244,7 +42244,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F80" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G80" t="n">
         <v>2.05868133214936</v>
@@ -42262,7 +42262,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="D81" t="n">
         <v>24.43126133466969</v>
@@ -42271,7 +42271,7 @@
         <v>24.43126133466969</v>
       </c>
       <c r="F81" t="n">
-        <v>50.29618163054695</v>
+        <v>50.29618163054696</v>
       </c>
       <c r="G81" t="n">
         <v>2.05868133214936</v>
@@ -48706,7 +48706,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D26" t="n">
         <v>19.28759329767769</v>
@@ -48715,7 +48715,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F26" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G26" t="n">
         <v>11.57427084076214</v>
@@ -48733,7 +48733,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D27" t="n">
         <v>19.28759329767769</v>
@@ -48742,7 +48742,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F27" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G27" t="n">
         <v>11.57427084076214</v>
@@ -48760,7 +48760,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D28" t="n">
         <v>19.28759329767769</v>
@@ -48769,7 +48769,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F28" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G28" t="n">
         <v>11.57427084076214</v>
@@ -48787,7 +48787,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D29" t="n">
         <v>19.28759329767769</v>
@@ -48796,7 +48796,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F29" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G29" t="n">
         <v>11.57427084076214</v>
@@ -48814,7 +48814,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D30" t="n">
         <v>19.28759329767769</v>
@@ -48823,7 +48823,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F30" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G30" t="n">
         <v>11.57427084076214</v>
@@ -48841,7 +48841,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D31" t="n">
         <v>19.28759329767769</v>
@@ -48850,7 +48850,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F31" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G31" t="n">
         <v>11.57427084076214</v>
@@ -48868,7 +48868,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D32" t="n">
         <v>19.28759329767769</v>
@@ -48877,7 +48877,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F32" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G32" t="n">
         <v>11.57427084076214</v>
@@ -48895,7 +48895,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D33" t="n">
         <v>19.28759329767769</v>
@@ -48904,7 +48904,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F33" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G33" t="n">
         <v>11.57427084076214</v>
@@ -48922,7 +48922,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D34" t="n">
         <v>19.28759329767769</v>
@@ -48931,7 +48931,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F34" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G34" t="n">
         <v>11.57427084076214</v>
@@ -48949,7 +48949,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D35" t="n">
         <v>19.28759329767769</v>
@@ -48958,7 +48958,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F35" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G35" t="n">
         <v>11.57427084076214</v>
@@ -48976,7 +48976,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D36" t="n">
         <v>19.28759329767769</v>
@@ -48985,7 +48985,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F36" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G36" t="n">
         <v>11.57427084076214</v>
@@ -49003,7 +49003,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D37" t="n">
         <v>19.28759329767769</v>
@@ -49012,7 +49012,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F37" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G37" t="n">
         <v>11.57427084076214</v>
@@ -49030,7 +49030,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D38" t="n">
         <v>19.28759329767769</v>
@@ -49039,7 +49039,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F38" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G38" t="n">
         <v>11.57427084076214</v>
@@ -49057,7 +49057,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D39" t="n">
         <v>19.28759329767769</v>
@@ -49066,7 +49066,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F39" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G39" t="n">
         <v>11.57427084076214</v>
@@ -49084,7 +49084,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D40" t="n">
         <v>19.28759329767769</v>
@@ -49093,7 +49093,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F40" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G40" t="n">
         <v>11.57427084076214</v>
@@ -49111,7 +49111,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="D41" t="n">
         <v>19.28759329767769</v>
@@ -49120,7 +49120,7 @@
         <v>19.28759329767769</v>
       </c>
       <c r="F41" t="n">
-        <v>223.2398286937902</v>
+        <v>223.2398286937901</v>
       </c>
       <c r="G41" t="n">
         <v>11.57427084076214</v>
@@ -50230,7 +50230,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G82" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="83">
@@ -50257,7 +50257,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G83" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="84">
@@ -50284,7 +50284,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G84" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="85">
@@ -50311,7 +50311,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G85" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="86">
@@ -50338,7 +50338,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G86" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="87">
@@ -50365,7 +50365,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G87" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="88">
@@ -50392,7 +50392,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G88" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="89">
@@ -50419,7 +50419,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G89" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="90">
@@ -50446,7 +50446,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G90" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="91">
@@ -50473,7 +50473,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G91" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="92">
@@ -50500,7 +50500,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G92" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="93">
@@ -50527,7 +50527,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G93" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="94">
@@ -50554,7 +50554,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G94" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="95">
@@ -50581,7 +50581,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G95" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="96">
@@ -50608,7 +50608,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G96" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
     <row r="97">
@@ -50635,7 +50635,7 @@
         <v>153.9025695931478</v>
       </c>
       <c r="G97" t="n">
-        <v>7.886098405514566</v>
+        <v>7.886098405514568</v>
       </c>
     </row>
   </sheetData>
